--- a/Hoadon/HD2026/HDVao/5/001065010300_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/5/001065010300_HDDienTuDaCapMa.xlsx
@@ -314,6 +314,172 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C26TPM</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502547345</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ KHANG PHÚC MINH</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>HKD HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>18/6 Phước Bình, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>4009091.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>400909.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>4410000.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C26TPM</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502547345</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ KHANG PHÚC MINH</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>HKD HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>18/6 Phước Bình, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>2727273.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>272727.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
